--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.91545502174434</v>
+        <v>3.073761441033455</v>
       </c>
       <c r="D2" t="n">
-        <v>12.83683172375882</v>
+        <v>2.085985155110809</v>
       </c>
       <c r="E2" t="n">
-        <v>8.166830581762346</v>
+        <v>1.327109969536381</v>
       </c>
       <c r="F2" t="n">
-        <v>7.436169987591725</v>
+        <v>1.208377622983656</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.216645382740583</v>
+        <v>0.3602048746953448</v>
       </c>
       <c r="D3" t="n">
-        <v>2.001807564606306</v>
+        <v>0.3252937292485248</v>
       </c>
       <c r="E3" t="n">
-        <v>8.166830581762346</v>
+        <v>1.327109969536381</v>
       </c>
       <c r="F3" t="n">
-        <v>7.436169987591725</v>
+        <v>1.208377622983656</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.10540895221489</v>
+        <v>3.26712895473492</v>
       </c>
       <c r="D4" t="n">
-        <v>20.09948119609331</v>
+        <v>3.266165694365164</v>
       </c>
       <c r="E4" t="n">
-        <v>8.166830581762346</v>
+        <v>1.327109969536381</v>
       </c>
       <c r="F4" t="n">
-        <v>7.436169987591725</v>
+        <v>1.208377622983656</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
